--- a/グラフ・表系メモ.xlsx
+++ b/グラフ・表系メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programs\XmlWriter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19152A6-23AE-4D9B-B640-962E84367B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13BA3AE-23CA-47A1-88EC-93C417008B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{5D7DA2A5-53FF-43D1-8583-82CF21C04067}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>色</t>
     <rPh sb="0" eb="1">
@@ -232,49 +232,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ランプ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アグロ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コントロール</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>序盤から継続的に削れていれば決着。少しの妨害で容易にキルターンが遅れる。</t>
-    <rPh sb="0" eb="2">
-      <t>ジョバン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ケイゾク</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ケズ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ケッチャク</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ボウガイ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ヨウイ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>オク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>10, 10</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -306,6 +263,69 @@
     </rPh>
     <rPh sb="44" eb="46">
       <t>テイソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無</t>
+    <rPh sb="0" eb="1">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒アグロ</t>
+    <rPh sb="0" eb="1">
+      <t>クロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒コントロール</t>
+    <rPh sb="0" eb="1">
+      <t>クロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マナ加速なし</t>
+    <rPh sb="2" eb="4">
+      <t>カソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グラフ比較用</t>
+    <rPh sb="3" eb="6">
+      <t>ヒカクヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒ミッドレンジ</t>
+    <rPh sb="0" eb="1">
+      <t>クロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>緑ミッドレンジ</t>
+    <rPh sb="0" eb="1">
+      <t>ミドリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4, 4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>序盤から継続的に削れていれば決着。少しの妨害で容易にキルターンが遅れる。</t>
+  </si>
+  <si>
+    <t>基準値。</t>
+    <rPh sb="0" eb="3">
+      <t>キジュンチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -385,8 +405,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B06EDA3C-CA80-4356-A3BD-0C05F2206700}" name="テーブル1" displayName="テーブル1" ref="B3:Z6" totalsRowShown="0">
-  <autoFilter ref="B3:Z6" xr:uid="{B06EDA3C-CA80-4356-A3BD-0C05F2206700}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B06EDA3C-CA80-4356-A3BD-0C05F2206700}" name="テーブル1" displayName="テーブル1" ref="B3:Z8" totalsRowShown="0">
+  <autoFilter ref="B3:Z8" xr:uid="{B06EDA3C-CA80-4356-A3BD-0C05F2206700}"/>
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{3B396D90-49AF-410E-B661-9762AE7996A2}" name="色"/>
     <tableColumn id="25" xr3:uid="{E709E10A-F2EB-48FE-BCF2-6B337587B460}" name="デッキタイプ"/>
@@ -398,7 +418,7 @@
     </tableColumn>
     <tableColumn id="6" xr3:uid="{22365318-2C81-4578-BF91-C33DB75EB6C0}" name="想定勝利ターン数"/>
     <tableColumn id="7" xr3:uid="{BA7258AA-D7F5-4BEC-8862-5B5A7B307025}" name="#マナ加速量">
-      <calculatedColumnFormula>テーブル1[[#This Row],[決着時マナ合計]]-テーブル1[[#This Row],[想定勝利ターン数]]</calculatedColumnFormula>
+      <calculatedColumnFormula>テーブル1[[#This Row],[決着時マナ合計]]-(テーブル1[[#This Row],[想定勝利ターン数]]*2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{29172D22-3387-4468-B613-2C19301E9640}" name="#マナ加速量ターン平均">
       <calculatedColumnFormula>テーブル1[[#This Row],['#マナ加速量]]/テーブル1[[#This Row],[想定勝利ターン数]]</calculatedColumnFormula>
@@ -741,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D4D5416-1585-4DF1-B9F9-7C6270445BD7}">
-  <dimension ref="B3:Z6"/>
+  <dimension ref="B3:Z8"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7.25" customWidth="1"/>
@@ -838,78 +858,156 @@
     </row>
     <row r="4" spans="2:26" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G4">
         <f>テーブル1[[#This Row],[決着時マナ合計]]/テーブル1[[#This Row],[マスの数]]</f>
-        <v>3.5</v>
+        <v>24</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I4">
-        <f>テーブル1[[#This Row],[決着時マナ合計]]-テーブル1[[#This Row],[想定勝利ターン数]]</f>
-        <v>13</v>
+        <f>テーブル1[[#This Row],[決着時マナ合計]]-(テーブル1[[#This Row],[想定勝利ターン数]]*2)</f>
+        <v>0</v>
       </c>
       <c r="J4">
         <f>テーブル1[[#This Row],['#マナ加速量]]/テーブル1[[#This Row],[想定勝利ターン数]]</f>
-        <v>1.625</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>80</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>28</v>
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>2</v>
+      </c>
+      <c r="P4">
+        <v>4</v>
+      </c>
+      <c r="Q4">
+        <v>6</v>
+      </c>
+      <c r="R4">
+        <v>8</v>
+      </c>
+      <c r="S4">
+        <v>10</v>
+      </c>
+      <c r="T4">
+        <v>12</v>
+      </c>
+      <c r="U4">
+        <v>14</v>
+      </c>
+      <c r="V4">
+        <v>16</v>
+      </c>
+      <c r="W4">
+        <v>18</v>
+      </c>
+      <c r="X4">
+        <v>20</v>
+      </c>
+      <c r="Y4">
+        <v>22</v>
+      </c>
+      <c r="Z4">
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="2:26" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G5">
         <f>テーブル1[[#This Row],[決着時マナ合計]]/テーブル1[[#This Row],[マスの数]]</f>
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <f>テーブル1[[#This Row],[決着時マナ合計]]-テーブル1[[#This Row],[想定勝利ターン数]]</f>
+        <f>テーブル1[[#This Row],[決着時マナ合計]]-(テーブル1[[#This Row],[想定勝利ターン数]]*2)</f>
         <v>9</v>
       </c>
       <c r="J5">
         <f>テーブル1[[#This Row],['#マナ加速量]]/テーブル1[[#This Row],[想定勝利ターン数]]</f>
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K5">
-        <v>65</v>
-      </c>
-      <c r="L5" t="s">
-        <v>33</v>
+        <v>80</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+      <c r="P5">
+        <v>8</v>
+      </c>
+      <c r="Q5">
+        <v>10</v>
+      </c>
+      <c r="R5">
+        <v>12</v>
+      </c>
+      <c r="S5">
+        <v>20</v>
+      </c>
+      <c r="T5">
+        <v>21</v>
+      </c>
+      <c r="U5">
+        <v>21</v>
+      </c>
+      <c r="V5">
+        <v>21</v>
+      </c>
+      <c r="W5">
+        <v>21</v>
+      </c>
+      <c r="X5">
+        <v>21</v>
+      </c>
+      <c r="Y5">
+        <v>21</v>
+      </c>
+      <c r="Z5">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.4">
@@ -917,37 +1015,230 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <f>テーブル1[[#This Row],[決着時マナ合計]]/テーブル1[[#This Row],[マスの数]]</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <f>テーブル1[[#This Row],[決着時マナ合計]]-テーブル1[[#This Row],[想定勝利ターン数]]</f>
-        <v>10</v>
+        <f>テーブル1[[#This Row],[決着時マナ合計]]-(テーブル1[[#This Row],[想定勝利ターン数]]*2)</f>
+        <v>0</v>
       </c>
       <c r="J6">
         <f>テーブル1[[#This Row],['#マナ加速量]]/テーブル1[[#This Row],[想定勝利ターン数]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
+        <v>65</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <v>5</v>
+      </c>
+      <c r="Q6">
+        <v>7</v>
+      </c>
+      <c r="R6">
+        <v>8</v>
+      </c>
+      <c r="S6">
+        <v>8</v>
+      </c>
+      <c r="T6">
+        <v>8</v>
+      </c>
+      <c r="U6">
+        <v>8</v>
+      </c>
+      <c r="V6">
+        <v>8</v>
+      </c>
+      <c r="W6">
+        <v>8</v>
+      </c>
+      <c r="X6">
+        <v>8</v>
+      </c>
+      <c r="Y6">
+        <v>8</v>
+      </c>
+      <c r="Z6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <f>テーブル1[[#This Row],[決着時マナ合計]]/テーブル1[[#This Row],[マスの数]]</f>
+        <v>7.5</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <f>テーブル1[[#This Row],[決着時マナ合計]]-(テーブル1[[#This Row],[想定勝利ターン数]]*2)</f>
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <f>テーブル1[[#This Row],['#マナ加速量]]/テーブル1[[#This Row],[想定勝利ターン数]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="K7">
+        <v>80</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>6</v>
+      </c>
+      <c r="Q7">
+        <v>9</v>
+      </c>
+      <c r="R7">
+        <v>12</v>
+      </c>
+      <c r="S7">
+        <v>15</v>
+      </c>
+      <c r="T7">
+        <v>16</v>
+      </c>
+      <c r="U7">
+        <v>16</v>
+      </c>
+      <c r="V7">
+        <v>16</v>
+      </c>
+      <c r="W7">
+        <v>16</v>
+      </c>
+      <c r="X7">
+        <v>16</v>
+      </c>
+      <c r="Y7">
+        <v>16</v>
+      </c>
+      <c r="Z7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <f>テーブル1[[#This Row],[決着時マナ合計]]/テーブル1[[#This Row],[マスの数]]</f>
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <f>テーブル1[[#This Row],[決着時マナ合計]]-(テーブル1[[#This Row],[想定勝利ターン数]]*2)</f>
+        <v>4</v>
+      </c>
+      <c r="J8">
+        <f>テーブル1[[#This Row],['#マナ加速量]]/テーブル1[[#This Row],[想定勝利ターン数]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="K8">
         <v>90</v>
       </c>
-      <c r="L6" t="s">
-        <v>35</v>
+      <c r="L8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>3</v>
+      </c>
+      <c r="P8">
+        <v>6</v>
+      </c>
+      <c r="Q8">
+        <v>9</v>
+      </c>
+      <c r="R8">
+        <v>12</v>
+      </c>
+      <c r="S8">
+        <v>15</v>
+      </c>
+      <c r="T8">
+        <v>18</v>
+      </c>
+      <c r="U8">
+        <v>19</v>
+      </c>
+      <c r="V8">
+        <v>20</v>
+      </c>
+      <c r="W8">
+        <v>20</v>
+      </c>
+      <c r="X8">
+        <v>20</v>
+      </c>
+      <c r="Y8">
+        <v>20</v>
+      </c>
+      <c r="Z8">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
